--- a/artfynd/A 48318-2024 artfynd.xlsx
+++ b/artfynd/A 48318-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,27 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119281721</v>
+        <v>119281733</v>
       </c>
       <c r="B2" t="n">
-        <v>57461</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103020</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Entita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile palustris</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -708,16 +703,12 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -727,13 +718,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581446</v>
+        <v>581444</v>
       </c>
       <c r="R2" t="n">
-        <v>6426369</v>
+        <v>6426393</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -763,6 +754,11 @@
       <c r="AA2" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Spår av födosök</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -789,37 +785,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119281704</v>
+        <v>119281742</v>
       </c>
       <c r="B3" t="n">
-        <v>57463</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -831,7 +822,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>upprörd, varnande</t>
+          <t>gammalt bo</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -841,10 +832,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>581479</v>
+        <v>581358</v>
       </c>
       <c r="R3" t="n">
-        <v>6426338</v>
+        <v>6426391</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -877,6 +868,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I asp</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -903,15 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119281733</v>
+        <v>119281721</v>
       </c>
       <c r="B4" t="n">
-        <v>57326</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58112</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -919,16 +910,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>103020</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Entita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile palustris</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -936,12 +927,16 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>upprörd, varnande</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -951,13 +946,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>581444</v>
+        <v>581446</v>
       </c>
       <c r="R4" t="n">
-        <v>6426393</v>
+        <v>6426369</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,11 +982,6 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-08-22</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Spår av födosök</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1015,6 +1005,115 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119281704</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58114</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>A 34396, Ryven, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>581479</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6426338</v>
+      </c>
+      <c r="S5" t="n">
+        <v>25</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lofta</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-22</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Magnus Kasselstrand</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
